--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-418.7%</t>
+          <t>-418.8%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.2235393782135</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.23116753741605</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382333</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495504</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.299136146347061</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130023</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.31588437417825</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207819</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310988</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.30584953900654</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.31108639130943</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970911</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330528</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.421894867663105</v>
+        <v>3.421894867663107</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.571148963481575</v>
+        <v>-2.571879471308824</v>
       </c>
       <c r="E1919" t="n">
-        <v>2.048351806733578</v>
+        <v>2.048059603602678</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1231086696325563</v>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-64.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.4%</t>
+          <t>507.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-418.8%</t>
+          <t>-432.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-219.2%</t>
+          <t>-222.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.4%</t>
+          <t>-176.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-296.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.0%</t>
+          <t>-153.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.7%</t>
+          <t>-224.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-130.9%</t>
+          <t>-138.7%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-1.050027851145666</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.696552702669851</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>0.9935030990045379</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.713022126844588</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.389186228734188</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.553973650940891</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.6543447214160159</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.502611399597924</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.717203450461667</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.443105051988668</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.3263274996885367</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.326139356300204</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23116753741605</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.58445690696777</v>
+        <v>-1.713866703952696</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.504302419794795</v>
+        <v>2.452538501000825</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4584293290924942</v>
+        <v>0.3290195321075681</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.413499204351147</v>
+        <v>3.335853326160191</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382333</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.951167958634316</v>
+        <v>-2.080577755619242</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.358724391171909</v>
+        <v>2.306960472377939</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.03769151955897754</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.194578965394952</v>
+        <v>3.116933087203996</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495504</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.336348349564388</v>
+        <v>-2.465758146549314</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.203194773612744</v>
+        <v>2.151430854818773</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.03769151955897754</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.193121504207815</v>
+        <v>3.11547562601686</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347061</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.680031122791051</v>
+        <v>-2.809440919775977</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.067490787776695</v>
+        <v>2.015726868982724</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.01618777460126958</v>
+        <v>-0.1455975715861957</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.130146996446101</v>
+        <v>3.052501118255145</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.037681473029399</v>
+        <v>-3.167091270014325</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.920536706337613</v>
+        <v>1.868772787543643</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5032479218245438</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.911662844959349</v>
+        <v>2.834016966768394</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417825</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.044342413251547</v>
+        <v>-3.173752210236473</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.919645256949013</v>
+        <v>1.867881338155043</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5032479218245438</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.913435771659609</v>
+        <v>2.835789893468653</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.476148206401334</v>
+        <v>-3.60555800338626</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.733255827156503</v>
+        <v>1.681491908362532</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5102556212808846</v>
+        <v>-0.6396654182658108</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.817918161262253</v>
+        <v>2.740272283071298</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.802580735269078</v>
+        <v>-3.931990532254004</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.590967590611496</v>
+        <v>1.539203671817526</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7221336687729589</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.756721985960055</v>
+        <v>2.6790761077691</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900654</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.804144886379381</v>
+        <v>-3.933554683364307</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.58892252182334</v>
+        <v>1.53715860302937</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7221336687729589</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.75530257761602</v>
+        <v>2.677656699425064</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130943</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.167771131279694</v>
+        <v>-4.29718092826462</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.449959584097456</v>
+        <v>1.398195665303486</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6909455086551586</v>
+        <v>-0.8203553056400847</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.702857155729986</v>
+        <v>2.625211277539031</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970911</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.165344066750976</v>
+        <v>-4.294753863735902</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.450184924914775</v>
+        <v>1.398421006120805</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6912782904623102</v>
+        <v>-0.8206880874472364</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.701912001651527</v>
+        <v>2.624266123460571</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330528</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.573932843931654</v>
+        <v>-4.703342640916579</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.285510958057263</v>
+        <v>1.233747039263293</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.455520279357879</v>
+        <v>2.377874401166923</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.986915328072748</v>
+        <v>-5.116325125057673</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.115503396872286</v>
+        <v>1.063739478078316</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.45070571182934</v>
+        <v>2.373059833638384</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.403307202359746</v>
+        <v>-5.532716999344671</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9469406977663639</v>
+        <v>0.8951767789723939</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.448699762438217</v>
+        <v>2.371053884247261</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.77998421288959</v>
+        <v>-5.909394009874515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8065285842231051</v>
+        <v>0.7547646654291351</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.458958453106896</v>
+        <v>2.38131257491594</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.793699077214701</v>
+        <v>-5.923108874199627</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7971422036387561</v>
+        <v>0.7453782848447861</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.455058018252591</v>
+        <v>2.377412140061635</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.106523876459681</v>
+        <v>-6.235933673444606</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6704172039957652</v>
+        <v>0.6186532852017952</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.453462938307592</v>
+        <v>2.375817060116636</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.111336914925018</v>
+        <v>-6.240746711909943</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6722709645388383</v>
+        <v>0.6205070457448683</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.456313933415128</v>
+        <v>2.378668055224173</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.544686023035254</v>
+        <v>-6.674095820020179</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4949050167603408</v>
+        <v>0.4431410979663708</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.452287628880725</v>
+        <v>2.374641750689769</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.927687411777885</v>
+        <v>-7.05709720876281</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3416023599417044</v>
+        <v>0.2898384411477344</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.452185527559141</v>
+        <v>2.374539649368185</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.302672737949162</v>
+        <v>-7.432082534934088</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1941797454446235</v>
+        <v>0.1424158266506534</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.605808825501978</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.229765847827805</v>
+        <v>2.152119969636849</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.662203060453164</v>
+        <v>-7.791612857438089</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0557179197410731</v>
+        <v>0.003954000947103076</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.605808825501978</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.235116151125855</v>
+        <v>2.1574702729349</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.988603089118177</v>
+        <v>-8.118012886103102</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06692607176775445</v>
+        <v>-0.1186899905617245</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.802799057182065</v>
+        <v>-1.932208854166991</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.047192153884025</v>
+        <v>1.96954627569307</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.982126942324618</v>
+        <v>-8.111536739309543</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06129386242856194</v>
+        <v>-0.113057781222532</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.925732707373431</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.05411959258193</v>
+        <v>1.976473714390974</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.978436017368206</v>
+        <v>-8.107845814353132</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.0598174924459971</v>
+        <v>-0.1115814112399676</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.925732707373431</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.05411959258193</v>
+        <v>1.976473714390974</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.182694192698069</v>
+        <v>-8.312103989682996</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360075654593</v>
+        <v>-0.1877714842532709</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.923961855002494</v>
+        <v>-2.05337165198742</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.983049422932178</v>
+        <v>1.905403544741223</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.343333219186434</v>
+        <v>-8.472743016171361</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.19578062157021</v>
+        <v>-0.2475445403641809</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.03869532800489</v>
+        <v>-2.168105124989816</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.918691893615177</v>
+        <v>1.841046015424222</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.269863387518985</v>
+        <v>-8.399273184503912</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1510209874098094</v>
+        <v>-0.2027849062037799</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.965225496337441</v>
+        <v>-2.094635293322368</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978145494109068</v>
+        <v>1.900499615918112</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.444987804905528</v>
+        <v>-8.574397601890455</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2065155336169098</v>
+        <v>-0.2582794524108807</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.269759710708911</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.887626064424658</v>
+        <v>1.809980186233702</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.679439898920018</v>
+        <v>-8.808849695904945</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3075155361243018</v>
+        <v>-0.3592794549182723</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.269759710708911</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.880406899523062</v>
+        <v>1.802761021332106</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.967243743457256</v>
+        <v>-9.096653540442183</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4293092647131735</v>
+        <v>-0.481073183507144</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.428153758261223</v>
+        <v>-2.55756355524615</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.701052402026743</v>
+        <v>1.623406523835787</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.197068190621081</v>
+        <v>-9.326477987606008</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.520123253740147</v>
+        <v>-0.5718871725341179</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.590801295331384</v>
+        <v>-2.72021109231631</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.604579669623203</v>
+        <v>1.526933791432247</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.429097110357343</v>
+        <v>-9.55850690734227</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6102410930055373</v>
+        <v>-0.6620050117995078</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.570065779939264</v>
+        <v>1.492419901748308</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.37708159638853</v>
+        <v>-9.506491393373457</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5854445517316109</v>
+        <v>-0.6372084705255818</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.574056115625664</v>
+        <v>1.496410237434709</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.51875343811265</v>
+        <v>-9.648163235097577</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6435885153200007</v>
+        <v>-0.6953524341139716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.572580888726923</v>
+        <v>1.494935010535967</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.617660178571926</v>
+        <v>-9.747069975556853</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6680978013388388</v>
+        <v>-0.7198617201328097</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.751720732979082</v>
+        <v>-2.881130529964009</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.52829025461623</v>
+        <v>1.450644376425274</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.418508071334827</v>
+        <v>-9.547917868319754</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.601488092090682</v>
+        <v>-0.6532520108846529</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.586398207029269</v>
+        <v>-2.715808004014196</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.614432636539435</v>
+        <v>1.536786758348479</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.192662918615415</v>
+        <v>-9.322072715600342</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5015709579667087</v>
+        <v>-0.5533348767606796</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.544471531442105</v>
+        <v>-2.673881328427032</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.649167714927942</v>
+        <v>1.571521836736986</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.90638810629272</v>
+        <v>-9.035797903277647</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3859218884815721</v>
+        <v>-0.4376858072755425</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.544471531442105</v>
+        <v>-2.673881328427032</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.650306859484001</v>
+        <v>1.572660981293045</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.679592279219387</v>
+        <v>-8.809002076204314</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2925697834901309</v>
+        <v>-0.3443337022841018</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.476357586820561</v>
+        <v>-2.605767383805488</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.693809000419035</v>
+        <v>1.616163122228079</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.395683548290638</v>
+        <v>-8.525093345275565</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1732725868799947</v>
+        <v>-0.2250365056739656</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.476357586820561</v>
+        <v>-2.605767383805488</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.699542704657672</v>
+        <v>1.621896826466716</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.148696298097686</v>
+        <v>-8.278106095082613</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.08421494919667927</v>
+        <v>-0.1359788679906502</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.837997792379578</v>
+        <v>1.760351914188621</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.884859430893617</v>
+        <v>-8.014269227878543</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.01143631637204079</v>
+        <v>-0.04032760242192968</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.82811431106667</v>
+        <v>1.750468432875714</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.617617630025221</v>
+        <v>-7.747027427010146</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.1164984762200256</v>
+        <v>0.06473455742605516</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.826279750567296</v>
+        <v>1.74863387237634</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.341808466624737</v>
+        <v>-7.471218263609662</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2265218266067586</v>
+        <v>0.1747579078127881</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.140351028348875</v>
+        <v>-2.269760825333802</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.879391020561076</v>
+        <v>1.801745142370119</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.072740878857757</v>
+        <v>-7.202150675842683</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3348173678590438</v>
+        <v>0.2830534490650733</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.871283440581896</v>
+        <v>-2.000693237566823</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.041500079366757</v>
+        <v>1.963854201175801</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.808680940534961</v>
+        <v>-6.938090737519887</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.42718102702641</v>
+        <v>0.3754171082324396</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.6072235022591</v>
+        <v>-1.736633299244027</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.186675726198682</v>
+        <v>2.109029848007726</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.101601317030123</v>
+        <v>-6.231011114015049</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7072258427680445</v>
+        <v>0.655461923974074</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.6072235022591</v>
+        <v>-1.736633299244027</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.183888692538381</v>
+        <v>2.106242814347425</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.851960287044171</v>
+        <v>-5.981370084029097</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8074258786502666</v>
+        <v>0.7556619598562966</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.357582472273148</v>
+        <v>-1.486992269258075</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.334016934417794</v>
+        <v>2.256371056226838</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.597418387703096</v>
+        <v>-5.726828184688021</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.9086094596074537</v>
+        <v>0.8568455408134836</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.103040572932072</v>
+        <v>-1.232450369916999</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.486108895243196</v>
+        <v>2.40846301705224</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.363937165473497</v>
+        <v>-5.493346962458422</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.009926377337146</v>
+        <v>0.9581624585431756</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8695593507024739</v>
+        <v>-0.9989691476874007</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.634122057418808</v>
+        <v>2.556476179227852</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.184228635329625</v>
+        <v>-5.31363843231455</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.078917579081736</v>
+        <v>1.027153660287766</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8123878465397778</v>
+        <v>-0.9417976435247046</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.665532749603466</v>
+        <v>2.58788687141251</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.051953161698738</v>
+        <v>-5.181362958683663</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.127195255281117</v>
+        <v>1.075431336487147</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6801123729088911</v>
+        <v>-0.809522169893818</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.740265520529025</v>
+        <v>2.662619642338069</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.861353487025585</v>
+        <v>-4.990763284010511</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.206250185838015</v>
+        <v>1.154486267044045</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4895126982357383</v>
+        <v>-0.6189224952206651</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.857440386020554</v>
+        <v>2.779794507829597</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.612353688342004</v>
+        <v>-4.741763485326929</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.318756446535106</v>
+        <v>1.266992527741136</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4895126982357383</v>
+        <v>-0.6189224952206651</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.870346727244212</v>
+        <v>2.792700849053256</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.717943678115109</v>
+        <v>-4.847353475100034</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.148544521026645</v>
+        <v>1.096780602232675</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5951026880088426</v>
+        <v>-0.7245124849937694</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.679016803781131</v>
+        <v>2.601370925590175</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.438916382459482</v>
+        <v>-4.568326179444407</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.308699781165983</v>
+        <v>1.256935862372013</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5951026880088426</v>
+        <v>-0.7245124849937694</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.727561145658217</v>
+        <v>2.649915267467261</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.162178207788669</v>
+        <v>-4.291588004773594</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.422774063020303</v>
+        <v>1.371010144226332</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4132860268989168</v>
+        <v>-0.5426958238838436</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.840030154310167</v>
+        <v>2.762384276119211</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.035285801353599</v>
+        <v>-4.164695598338524</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.464817039340852</v>
+        <v>1.413053120546882</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.907451611917731</v>
+        <v>2.829805733726775</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.847698293443672</v>
+        <v>-3.977108090428597</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.53289143040973</v>
+        <v>1.48112751161576</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.900490999822638</v>
+        <v>2.822845121631682</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.605549899989814</v>
+        <v>-3.734959696974739</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.644213142172416</v>
+        <v>1.592449223378446</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.914953354203781</v>
+        <v>2.837307476012825</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.542320528221465</v>
+        <v>-3.67173032520639</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.664037011338951</v>
+        <v>1.612273092544981</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.909485474662976</v>
+        <v>2.83183959647202</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.355832835844459</v>
+        <v>-3.485242632829384</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.73613018230033</v>
+        <v>1.68436626350636</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.09990592808684062</v>
+        <v>-0.2293157250717675</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.018876184099757</v>
+        <v>2.941230305908801</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.334683636941016</v>
+        <v>-3.464093433925941</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.752290840099033</v>
+        <v>1.700526921305063</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.07875672918339727</v>
+        <v>-0.2081665261683241</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.039266681679148</v>
+        <v>2.961620803488192</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.090918194957571</v>
+        <v>-3.220327991942496</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.845577725239461</v>
+        <v>1.793813806445491</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.07875672918339727</v>
+        <v>-0.2081665261683241</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.035047390026199</v>
+        <v>2.957401511835243</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.826890127764311</v>
+        <v>-2.956299924749236</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.953313266036782</v>
+        <v>1.901549347242812</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1231086696325563</v>
+        <v>-0.006301127352370539</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.158290943235787</v>
+        <v>3.080645065044831</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.421894867663107</v>
+        <v>3.719083791904226</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.571879471308824</v>
+        <v>-2.706449530800162</v>
       </c>
       <c r="E1919" t="n">
-        <v>2.048059603602678</v>
+        <v>1.994231579806144</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1231086696325563</v>
+        <v>-0.006301127352370539</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.151033018219489</v>
+        <v>3.073387140028534</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-12.7%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>507.5%</t>
+          <t>507.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-432.2%</t>
+          <t>-459.6%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-222.3%</t>
+          <t>-223.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-37.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.8%</t>
+          <t>-187.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-298.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-154.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.6%</t>
+          <t>-226.6%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-179.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.7%</t>
+          <t>-147.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1919"/>
+  <dimension ref="A1:G1920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.050027851145666</v>
+        <v>-1.069839233936604</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.696552702669851</v>
+        <v>2.688628149553476</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9935030990045379</v>
+        <v>0.9736917162136004</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.713022126844588</v>
+        <v>3.701135297170025</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.389186228734188</v>
+        <v>-1.408997611525126</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.553973650940891</v>
+        <v>2.546049097824516</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6543447214160159</v>
+        <v>0.6345333386250783</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.502611399597924</v>
+        <v>3.490724569923361</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213499</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.717203450461667</v>
+        <v>-1.737014833252605</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.443105051988668</v>
+        <v>2.435180498872293</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3263274996885367</v>
+        <v>0.3065161168975992</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.326139356300204</v>
+        <v>3.314252526625642</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.713866703952696</v>
+        <v>-1.733678086743634</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.452538501000825</v>
+        <v>2.44461394788445</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3290195321075681</v>
+        <v>0.3092081493166305</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.335853326160191</v>
+        <v>3.323966496485629</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.080577755619242</v>
+        <v>-2.100389138410179</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.306960472377939</v>
+        <v>2.299035919261564</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03769151955897754</v>
+        <v>-0.05750290234991506</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.116933087203996</v>
+        <v>3.105046257529434</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.465758146549314</v>
+        <v>-2.485569529340252</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.151430854818773</v>
+        <v>2.143506301702398</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03769151955897754</v>
+        <v>-0.05750290234991506</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.11547562601686</v>
+        <v>3.103588796342297</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.809440919775977</v>
+        <v>-2.829252302566915</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.015726868982724</v>
+        <v>2.007802315866349</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1455975715861957</v>
+        <v>-0.1654089543771333</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.052501118255145</v>
+        <v>3.040614288580582</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130023</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.167091270014325</v>
+        <v>-3.186902652805263</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.868772787543643</v>
+        <v>1.860848234427267</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5032479218245438</v>
+        <v>-0.5230593046154814</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.834016966768394</v>
+        <v>2.822130137093831</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.173752210236473</v>
+        <v>-3.19356359302741</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.867881338155043</v>
+        <v>1.859956785038668</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5032479218245438</v>
+        <v>-0.5230593046154814</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.835789893468653</v>
+        <v>2.823903063794091</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.60555800338626</v>
+        <v>-3.625369386177198</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.681491908362532</v>
+        <v>1.673567355246157</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6396654182658108</v>
+        <v>-0.6594768010567484</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.740272283071298</v>
+        <v>2.728385453396735</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.931990532254004</v>
+        <v>-3.951801915044942</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.539203671817526</v>
+        <v>1.53127911870115</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7221336687729589</v>
+        <v>-0.7419450515638966</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6790761077691</v>
+        <v>2.667189278094537</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.933554683364307</v>
+        <v>-3.953366066155245</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.53715860302937</v>
+        <v>1.529234049912994</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7221336687729589</v>
+        <v>-0.7419450515638966</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.677656699425064</v>
+        <v>2.665769869750502</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.29718092826462</v>
+        <v>-4.316992311055557</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.398195665303486</v>
+        <v>1.390271112187111</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8203553056400847</v>
+        <v>-0.8401666884310224</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.625211277539031</v>
+        <v>2.613324447864468</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.294753863735902</v>
+        <v>-4.314565246526839</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.398421006120805</v>
+        <v>1.390496453004429</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8206880874472364</v>
+        <v>-0.8404994702381741</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.624266123460571</v>
+        <v>2.612379293786009</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.703342640916579</v>
+        <v>-4.723154023707518</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.233747039263293</v>
+        <v>1.225822486146917</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.377874401166923</v>
+        <v>2.365987571492361</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.116325125057673</v>
+        <v>-5.136136507848612</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.063739478078316</v>
+        <v>1.05581492496194</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.373059833638384</v>
+        <v>2.361173003963821</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.532716999344671</v>
+        <v>-5.552528382135609</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8951767789723939</v>
+        <v>0.8872522258560185</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.371053884247261</v>
+        <v>2.359167054572699</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.909394009874515</v>
+        <v>-5.929205392665454</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7547646654291351</v>
+        <v>0.7468401123127597</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.38131257491594</v>
+        <v>2.369425745241378</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.923108874199627</v>
+        <v>-5.942920256990565</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7453782848447861</v>
+        <v>0.7374537317284102</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.377412140061635</v>
+        <v>2.365525310387073</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.235933673444606</v>
+        <v>-6.255745056235544</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6186532852017952</v>
+        <v>0.6107287320854193</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.249088247418852</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.375817060116636</v>
+        <v>2.363930230442074</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.240746711909943</v>
+        <v>-6.260558094700881</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6205070457448683</v>
+        <v>0.6125824926284928</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.250634882121638</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.378668055224173</v>
+        <v>2.366781225549611</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.674095820020179</v>
+        <v>-6.693907202811118</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4431410979663708</v>
+        <v>0.4352165448499949</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.250634882121638</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.374641750689769</v>
+        <v>2.362754921015207</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.05709720876281</v>
+        <v>-7.076908591553749</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2898384411477344</v>
+        <v>0.2819138880313585</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.250634882121638</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.374539649368185</v>
+        <v>2.362652819693623</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.432082534934088</v>
+        <v>-7.451893917725026</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1424158266506534</v>
+        <v>0.134491273534278</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.605808825501978</v>
+        <v>-1.625620208292916</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.152119969636849</v>
+        <v>2.140233139962287</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.791612857438089</v>
+        <v>-7.811424240229027</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.003954000947103076</v>
+        <v>-0.003970552169272779</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.605808825501978</v>
+        <v>-1.625620208292916</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.1574702729349</v>
+        <v>2.145583443260337</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.118012886103102</v>
+        <v>-8.13782426889404</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1186899905617245</v>
+        <v>-0.1266145436781003</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.932208854166991</v>
+        <v>-1.952020236957928</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96954627569307</v>
+        <v>1.957659446018507</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.111536739309543</v>
+        <v>-8.13134812210048</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.113057781222532</v>
+        <v>-0.1209823343389078</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.925732707373431</v>
+        <v>-1.945544090164369</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.976473714390974</v>
+        <v>1.964586884716411</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.107845814353132</v>
+        <v>-8.127657197144069</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1115814112399676</v>
+        <v>-0.1195059643563434</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.925732707373431</v>
+        <v>-1.945544090164369</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.976473714390974</v>
+        <v>1.964586884716411</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.312103989682996</v>
+        <v>-8.331915372473933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1877714842532709</v>
+        <v>-0.1956960373696464</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.05337165198742</v>
+        <v>-2.073183034778358</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.905403544741223</v>
+        <v>1.893516715066661</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.472743016171361</v>
+        <v>-8.492554398962298</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2475445403641809</v>
+        <v>-0.2554690934805564</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.168105124989816</v>
+        <v>-2.187916507780753</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.841046015424222</v>
+        <v>1.829159185749659</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.399273184503912</v>
+        <v>-8.419084567294849</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027849062037799</v>
+        <v>-0.2107094593201557</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.094635293322368</v>
+        <v>-2.114446676113305</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.900499615918112</v>
+        <v>1.888612786243549</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.574397601890455</v>
+        <v>-8.594208984681392</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582794524108807</v>
+        <v>-0.2662040055272561</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.269759710708911</v>
+        <v>-2.289571093499849</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.809980186233702</v>
+        <v>1.79809335655914</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.808849695904945</v>
+        <v>-8.828661078695882</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3592794549182723</v>
+        <v>-0.3672040080346481</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.269759710708911</v>
+        <v>-2.289571093499849</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.802761021332106</v>
+        <v>1.790874191657544</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.096653540442183</v>
+        <v>-9.116464923233121</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.481073183507144</v>
+        <v>-0.4889977366235199</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.55756355524615</v>
+        <v>-2.577374938037087</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.623406523835787</v>
+        <v>1.611519694161225</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.326477987606008</v>
+        <v>-9.346289370396946</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5718871725341179</v>
+        <v>-0.5798117256504933</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.72021109231631</v>
+        <v>-2.740022475107248</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.526933791432247</v>
+        <v>1.515046961757685</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.55850690734227</v>
+        <v>-9.578318290133208</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6620050117995078</v>
+        <v>-0.6699295649158836</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.802035172295671</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.492419901748308</v>
+        <v>1.480533072073746</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.506491393373457</v>
+        <v>-9.526302776164394</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6372084705255818</v>
+        <v>-0.6451330236419572</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.802035172295671</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.496410237434709</v>
+        <v>1.484523407760146</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.648163235097577</v>
+        <v>-9.667974617888515</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6953524341139716</v>
+        <v>-0.703276987230347</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.802035172295671</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.494935010535967</v>
+        <v>1.483048180861405</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.747069975556853</v>
+        <v>-9.76688135834779</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7198617201328097</v>
+        <v>-0.7277862732491851</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.881130529964009</v>
+        <v>-2.900941912754946</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.450644376425274</v>
+        <v>1.438757546750711</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.547917868319754</v>
+        <v>-9.567729251110691</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6532520108846529</v>
+        <v>-0.6611765640010288</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.715808004014196</v>
+        <v>-2.735619386805133</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.536786758348479</v>
+        <v>1.524899928673916</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.322072715600342</v>
+        <v>-9.341884098391281</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5533348767606796</v>
+        <v>-0.5612594298770559</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.673881328427032</v>
+        <v>-2.693692711217969</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.571521836736986</v>
+        <v>1.559635007062423</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.035797903277647</v>
+        <v>-9.055609286068586</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4376858072755425</v>
+        <v>-0.4456103603919188</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.673881328427032</v>
+        <v>-2.693692711217969</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.572660981293045</v>
+        <v>1.560774151618482</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.809002076204314</v>
+        <v>-8.828813458995253</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3443337022841018</v>
+        <v>-0.3522582554004781</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.605767383805488</v>
+        <v>-2.625578766596425</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.616163122228079</v>
+        <v>1.604276292553517</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.525093345275565</v>
+        <v>-8.544904728066504</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2250365056739656</v>
+        <v>-0.2329610587903419</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.605767383805488</v>
+        <v>-2.625578766596425</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.621896826466716</v>
+        <v>1.610009996792153</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.278106095082613</v>
+        <v>-8.297917477873552</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1359788679906502</v>
+        <v>-0.1439034211070265</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.378591516403473</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.760351914188621</v>
+        <v>1.748465084514059</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.014269227878543</v>
+        <v>-8.034080610669482</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.04032760242192968</v>
+        <v>-0.04825215553830597</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.378591516403473</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.750468432875714</v>
+        <v>1.738581603201151</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.747027427010146</v>
+        <v>-7.766838809801086</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.06473455742605516</v>
+        <v>0.05681000430967886</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.378591516403473</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.74863387237634</v>
+        <v>1.736747042701778</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.471218263609662</v>
+        <v>-7.491029646400602</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.1747579078127881</v>
+        <v>0.1668333546964118</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.269760825333802</v>
+        <v>-2.289572208124739</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.801745142370119</v>
+        <v>1.789858312695557</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.202150675842683</v>
+        <v>-7.221962058633622</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2830534490650733</v>
+        <v>0.275128895948697</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.000693237566823</v>
+        <v>-2.02050462035776</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.963854201175801</v>
+        <v>1.951967371501238</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.938090737519887</v>
+        <v>-6.957902120310826</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3754171082324396</v>
+        <v>0.3674925551160633</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.736633299244027</v>
+        <v>-1.756444682034964</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.109029848007726</v>
+        <v>2.097143018333164</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.231011114015049</v>
+        <v>-6.250822496805988</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.655461923974074</v>
+        <v>0.6475373708576977</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.736633299244027</v>
+        <v>-1.756444682034964</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.106242814347425</v>
+        <v>2.094355984672863</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.981370084029097</v>
+        <v>-6.001181466820036</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7556619598562966</v>
+        <v>0.7477374067399198</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.486992269258075</v>
+        <v>-1.506803652049012</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.256371056226838</v>
+        <v>2.244484226552276</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.726828184688021</v>
+        <v>-5.74663956747896</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8568455408134836</v>
+        <v>0.8489209876971073</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.232450369916999</v>
+        <v>-1.252261752707937</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.40846301705224</v>
+        <v>2.396576187377677</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.493346962458422</v>
+        <v>-5.513158345249361</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9581624585431756</v>
+        <v>0.9502379054267993</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9989691476874007</v>
+        <v>-1.018780530478338</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.556476179227852</v>
+        <v>2.544589349553289</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.31363843231455</v>
+        <v>-5.333449815105489</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.027153660287766</v>
+        <v>1.019229107171389</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9417976435247046</v>
+        <v>-0.961609026315642</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.58788687141251</v>
+        <v>2.576000041737947</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.181362958683663</v>
+        <v>-5.201174341474602</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.075431336487147</v>
+        <v>1.067506783370771</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.809522169893818</v>
+        <v>-0.8293335526847554</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.662619642338069</v>
+        <v>2.650732812663507</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.990763284010511</v>
+        <v>-5.01057466680145</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.154486267044045</v>
+        <v>1.146561713927668</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6189224952206651</v>
+        <v>-0.6387338780116025</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.779794507829597</v>
+        <v>2.767907678155035</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.741763485326929</v>
+        <v>-4.761574868117869</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.266992527741136</v>
+        <v>1.25906797462476</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6189224952206651</v>
+        <v>-0.6387338780116025</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.792700849053256</v>
+        <v>2.780814019378694</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.847353475100034</v>
+        <v>-4.867164857890973</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.096780602232675</v>
+        <v>1.088856049116299</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7245124849937694</v>
+        <v>-0.7443238677847068</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.601370925590175</v>
+        <v>2.589484095915612</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.568326179444407</v>
+        <v>-4.588137562235346</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.256935862372013</v>
+        <v>1.249011309255636</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7245124849937694</v>
+        <v>-0.7443238677847068</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.649915267467261</v>
+        <v>2.638028437792699</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.291588004773594</v>
+        <v>-4.311399387564533</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.371010144226332</v>
+        <v>1.363085591109956</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5426958238838436</v>
+        <v>-0.562507206674781</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.762384276119211</v>
+        <v>2.750497446444649</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.164695598338524</v>
+        <v>-4.184506981129463</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.413053120546882</v>
+        <v>1.405128567430506</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.4356148002397111</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.829805733726775</v>
+        <v>2.817918904052213</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.977108090428597</v>
+        <v>-3.996919473219536</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.48112751161576</v>
+        <v>1.473202958499384</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.4356148002397111</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.822845121631682</v>
+        <v>2.81095829195712</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.734959696974739</v>
+        <v>-3.754771079765678</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.592449223378446</v>
+        <v>1.58452467026207</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.4356148002397111</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.837307476012825</v>
+        <v>2.825420646338263</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.67173032520639</v>
+        <v>-3.69154170799733</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.612273092544981</v>
+        <v>1.604348539428604</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.4356148002397111</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.83183959647202</v>
+        <v>2.819952766797458</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.485242632829384</v>
+        <v>-3.505054015620323</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.68436626350636</v>
+        <v>1.676441710389984</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2293157250717675</v>
+        <v>-0.2491271078627049</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.941230305908801</v>
+        <v>2.929343476234238</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.464093433925941</v>
+        <v>-3.48390481671688</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.700526921305063</v>
+        <v>1.692602368188687</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2081665261683241</v>
+        <v>-0.2279779089592615</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.961620803488192</v>
+        <v>2.94973397381363</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.220327991942496</v>
+        <v>-3.240139374733435</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.793813806445491</v>
+        <v>1.785889253329115</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2081665261683241</v>
+        <v>-0.2279779089592615</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.957401511835243</v>
+        <v>2.945514682160681</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.956299924749236</v>
+        <v>-2.976111307540175</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.901549347242812</v>
+        <v>1.893624794126435</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.006301127352370539</v>
+        <v>-0.02611251014330795</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.080645065044831</v>
+        <v>3.068758235370269</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,45 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.719083791904226</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.706449530800162</v>
+        <v>-2.980720108508027</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.994231579806144</v>
+        <v>1.884523348722997</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.006301127352370539</v>
+        <v>-0.02611251014330795</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.073387140028534</v>
+        <v>3.061500310353971</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B1920" t="n">
+        <v>3.719302572004177</v>
+      </c>
+      <c r="C1920" t="n">
+        <v>2.989546842497354</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>-2.980720108508027</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>1.884523348722997</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>-0.02611251014330795</v>
+      </c>
+      <c r="G1920" t="n">
+        <v>2.982610639483722</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-65.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>507.4%</t>
+          <t>507.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-459.6%</t>
+          <t>-432.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-223.1%</t>
+          <t>-222.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.8%</t>
+          <t>-176.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-298.2%</t>
+          <t>-296.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.3%</t>
+          <t>-153.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.6%</t>
+          <t>-224.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-179.3%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.069839233936604</v>
+        <v>-1.050027851145666</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.688628149553476</v>
+        <v>2.696552702669851</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9736917162136004</v>
+        <v>0.9935030990045379</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.701135297170025</v>
+        <v>3.713022126844588</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.408997611525126</v>
+        <v>-1.389186228734188</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.546049097824516</v>
+        <v>2.553973650940891</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6345333386250783</v>
+        <v>0.6543447214160159</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.490724569923361</v>
+        <v>3.502611399597924</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213499</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.737014833252605</v>
+        <v>-1.717203450461667</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.435180498872293</v>
+        <v>2.443105051988668</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3065161168975992</v>
+        <v>0.3263274996885367</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.314252526625642</v>
+        <v>3.326139356300204</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.733678086743634</v>
+        <v>-1.713866703952696</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.44461394788445</v>
+        <v>2.452538501000825</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3092081493166305</v>
+        <v>0.3290195321075681</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.323966496485629</v>
+        <v>3.335853326160191</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.100389138410179</v>
+        <v>-2.080577755619242</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.299035919261564</v>
+        <v>2.306960472377939</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.05750290234991506</v>
+        <v>-0.03769151955897754</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.105046257529434</v>
+        <v>3.116933087203996</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.485569529340252</v>
+        <v>-2.465758146549314</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.143506301702398</v>
+        <v>2.151430854818773</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.05750290234991506</v>
+        <v>-0.03769151955897754</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.103588796342297</v>
+        <v>3.11547562601686</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.829252302566915</v>
+        <v>-2.809440919775977</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.007802315866349</v>
+        <v>2.015726868982724</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1654089543771333</v>
+        <v>-0.1455975715861957</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.040614288580582</v>
+        <v>3.052501118255145</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.186902652805263</v>
+        <v>-3.167091270014325</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.860848234427267</v>
+        <v>1.868772787543643</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5230593046154814</v>
+        <v>-0.5032479218245438</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.822130137093831</v>
+        <v>2.834016966768394</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.19356359302741</v>
+        <v>-3.173752210236473</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.859956785038668</v>
+        <v>1.867881338155043</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5230593046154814</v>
+        <v>-0.5032479218245438</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.823903063794091</v>
+        <v>2.835789893468653</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.625369386177198</v>
+        <v>-3.60555800338626</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.673567355246157</v>
+        <v>1.681491908362532</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6594768010567484</v>
+        <v>-0.6396654182658108</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.728385453396735</v>
+        <v>2.740272283071298</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.951801915044942</v>
+        <v>-3.931990532254004</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.53127911870115</v>
+        <v>1.539203671817526</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7419450515638966</v>
+        <v>-0.7221336687729589</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.667189278094537</v>
+        <v>2.6790761077691</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.953366066155245</v>
+        <v>-3.933554683364307</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.529234049912994</v>
+        <v>1.53715860302937</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7419450515638966</v>
+        <v>-0.7221336687729589</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.665769869750502</v>
+        <v>2.677656699425064</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.316992311055557</v>
+        <v>-4.29718092826462</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.390271112187111</v>
+        <v>1.398195665303486</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8401666884310224</v>
+        <v>-0.8203553056400847</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.613324447864468</v>
+        <v>2.625211277539031</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.314565246526839</v>
+        <v>-4.294753863735902</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.390496453004429</v>
+        <v>1.398421006120805</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8404994702381741</v>
+        <v>-0.8206880874472364</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.612379293786009</v>
+        <v>2.624266123460571</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.723154023707518</v>
+        <v>-4.703342640916579</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.225822486146917</v>
+        <v>1.233747039263293</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.365987571492361</v>
+        <v>2.377874401166923</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.136136507848612</v>
+        <v>-5.116325125057673</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.05581492496194</v>
+        <v>1.063739478078316</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.361173003963821</v>
+        <v>2.373059833638384</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.552528382135609</v>
+        <v>-5.532716999344671</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8872522258560185</v>
+        <v>0.8951767789723939</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.359167054572699</v>
+        <v>2.371053884247261</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.929205392665454</v>
+        <v>-5.909394009874515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7468401123127597</v>
+        <v>0.7547646654291351</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.369425745241378</v>
+        <v>2.38131257491594</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.942920256990565</v>
+        <v>-5.923108874199627</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7374537317284102</v>
+        <v>0.7453782848447861</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.365525310387073</v>
+        <v>2.377412140061635</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.255745056235544</v>
+        <v>-6.235933673444606</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6107287320854193</v>
+        <v>0.6186532852017952</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.249088247418852</v>
+        <v>-1.229276864627915</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.363930230442074</v>
+        <v>2.375817060116636</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.260558094700881</v>
+        <v>-6.240746711909943</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6125824926284928</v>
+        <v>0.6205070457448683</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.250634882121638</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.366781225549611</v>
+        <v>2.378668055224173</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.693907202811118</v>
+        <v>-6.674095820020179</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4352165448499949</v>
+        <v>0.4431410979663708</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.250634882121638</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.362754921015207</v>
+        <v>2.374641750689769</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.076908591553749</v>
+        <v>-7.05709720876281</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2819138880313585</v>
+        <v>0.2898384411477344</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.250634882121638</v>
+        <v>-1.230823499330701</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.362652819693623</v>
+        <v>2.374539649368185</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.451893917725026</v>
+        <v>-7.432082534934088</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.134491273534278</v>
+        <v>0.1424158266506534</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.625620208292916</v>
+        <v>-1.605808825501978</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.140233139962287</v>
+        <v>2.152119969636849</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.811424240229027</v>
+        <v>-7.791612857438089</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.003970552169272779</v>
+        <v>0.003954000947103076</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.625620208292916</v>
+        <v>-1.605808825501978</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.145583443260337</v>
+        <v>2.1574702729349</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.13782426889404</v>
+        <v>-8.118012886103102</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1266145436781003</v>
+        <v>-0.1186899905617245</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.952020236957928</v>
+        <v>-1.932208854166991</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.957659446018507</v>
+        <v>1.96954627569307</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.13134812210048</v>
+        <v>-8.111536739309543</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1209823343389078</v>
+        <v>-0.113057781222532</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.945544090164369</v>
+        <v>-1.925732707373431</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.964586884716411</v>
+        <v>1.976473714390974</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.127657197144069</v>
+        <v>-8.107845814353132</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1195059643563434</v>
+        <v>-0.1115814112399676</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.945544090164369</v>
+        <v>-1.925732707373431</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.964586884716411</v>
+        <v>1.976473714390974</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.331915372473933</v>
+        <v>-8.312103989682996</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1956960373696464</v>
+        <v>-0.1877714842532709</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.073183034778358</v>
+        <v>-2.05337165198742</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.893516715066661</v>
+        <v>1.905403544741223</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.492554398962298</v>
+        <v>-8.472743016171361</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2554690934805564</v>
+        <v>-0.2475445403641809</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.187916507780753</v>
+        <v>-2.168105124989816</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.829159185749659</v>
+        <v>1.841046015424222</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.419084567294849</v>
+        <v>-8.399273184503912</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2107094593201557</v>
+        <v>-0.2027849062037799</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.114446676113305</v>
+        <v>-2.094635293322368</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.888612786243549</v>
+        <v>1.900499615918112</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.594208984681392</v>
+        <v>-8.574397601890455</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2662040055272561</v>
+        <v>-0.2582794524108807</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.289571093499849</v>
+        <v>-2.269759710708911</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.79809335655914</v>
+        <v>1.809980186233702</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.828661078695882</v>
+        <v>-8.808849695904945</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3672040080346481</v>
+        <v>-0.3592794549182723</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.289571093499849</v>
+        <v>-2.269759710708911</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.790874191657544</v>
+        <v>1.802761021332106</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.116464923233121</v>
+        <v>-9.096653540442183</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4889977366235199</v>
+        <v>-0.481073183507144</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.577374938037087</v>
+        <v>-2.55756355524615</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.611519694161225</v>
+        <v>1.623406523835787</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.346289370396946</v>
+        <v>-9.326477987606008</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5798117256504933</v>
+        <v>-0.5718871725341179</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.740022475107248</v>
+        <v>-2.72021109231631</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.515046961757685</v>
+        <v>1.526933791432247</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.578318290133208</v>
+        <v>-9.55850690734227</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6699295649158836</v>
+        <v>-0.6620050117995078</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.802035172295671</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.480533072073746</v>
+        <v>1.492419901748308</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.526302776164394</v>
+        <v>-9.506491393373457</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6451330236419572</v>
+        <v>-0.6372084705255818</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.802035172295671</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.484523407760146</v>
+        <v>1.496410237434709</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.667974617888515</v>
+        <v>-9.648163235097577</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.703276987230347</v>
+        <v>-0.6953524341139716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.802035172295671</v>
+        <v>-2.782223789504733</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.483048180861405</v>
+        <v>1.494935010535967</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.76688135834779</v>
+        <v>-9.747069975556853</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7277862732491851</v>
+        <v>-0.7198617201328097</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.900941912754946</v>
+        <v>-2.881130529964009</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.438757546750711</v>
+        <v>1.450644376425274</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.567729251110691</v>
+        <v>-9.547917868319754</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6611765640010288</v>
+        <v>-0.6532520108846529</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.735619386805133</v>
+        <v>-2.715808004014196</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.524899928673916</v>
+        <v>1.536786758348479</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.341884098391281</v>
+        <v>-9.322072715600342</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5612594298770559</v>
+        <v>-0.5533348767606796</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.693692711217969</v>
+        <v>-2.673881328427032</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.559635007062423</v>
+        <v>1.571521836736986</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.055609286068586</v>
+        <v>-9.035797903277647</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4456103603919188</v>
+        <v>-0.4376858072755425</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.693692711217969</v>
+        <v>-2.673881328427032</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.560774151618482</v>
+        <v>1.572660981293045</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.828813458995253</v>
+        <v>-8.809002076204314</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3522582554004781</v>
+        <v>-0.3443337022841018</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.625578766596425</v>
+        <v>-2.605767383805488</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.604276292553517</v>
+        <v>1.616163122228079</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.544904728066504</v>
+        <v>-8.525093345275565</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2329610587903419</v>
+        <v>-0.2250365056739656</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.625578766596425</v>
+        <v>-2.605767383805488</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.610009996792153</v>
+        <v>1.621896826466716</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.297917477873552</v>
+        <v>-8.278106095082613</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1439034211070265</v>
+        <v>-0.1359788679906502</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.378591516403473</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.748465084514059</v>
+        <v>1.760351914188621</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.034080610669482</v>
+        <v>-8.014269227878543</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.04825215553830597</v>
+        <v>-0.04032760242192968</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.378591516403473</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738581603201151</v>
+        <v>1.750468432875714</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.766838809801086</v>
+        <v>-7.747027427010146</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.05681000430967886</v>
+        <v>0.06473455742605516</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.378591516403473</v>
+        <v>-2.358780133612536</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736747042701778</v>
+        <v>1.74863387237634</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.491029646400602</v>
+        <v>-7.471218263609662</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.1668333546964118</v>
+        <v>0.1747579078127881</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.289572208124739</v>
+        <v>-2.269760825333802</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.789858312695557</v>
+        <v>1.801745142370119</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.221962058633622</v>
+        <v>-7.202150675842683</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.275128895948697</v>
+        <v>0.2830534490650733</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.02050462035776</v>
+        <v>-2.000693237566823</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.951967371501238</v>
+        <v>1.963854201175801</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.957902120310826</v>
+        <v>-6.938090737519887</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3674925551160633</v>
+        <v>0.3754171082324396</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.756444682034964</v>
+        <v>-1.736633299244027</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.097143018333164</v>
+        <v>2.109029848007726</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.250822496805988</v>
+        <v>-6.231011114015049</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6475373708576977</v>
+        <v>0.655461923974074</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.756444682034964</v>
+        <v>-1.736633299244027</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.094355984672863</v>
+        <v>2.106242814347425</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.001181466820036</v>
+        <v>-5.981370084029097</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7477374067399198</v>
+        <v>0.7556619598562966</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.506803652049012</v>
+        <v>-1.486992269258075</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.244484226552276</v>
+        <v>2.256371056226838</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.74663956747896</v>
+        <v>-5.726828184688021</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8489209876971073</v>
+        <v>0.8568455408134836</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.252261752707937</v>
+        <v>-1.232450369916999</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.396576187377677</v>
+        <v>2.40846301705224</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.513158345249361</v>
+        <v>-5.493346962458422</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9502379054267993</v>
+        <v>0.9581624585431756</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.018780530478338</v>
+        <v>-0.9989691476874007</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.544589349553289</v>
+        <v>2.556476179227852</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.333449815105489</v>
+        <v>-5.31363843231455</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.019229107171389</v>
+        <v>1.027153660287766</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.961609026315642</v>
+        <v>-0.9417976435247046</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.576000041737947</v>
+        <v>2.58788687141251</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.201174341474602</v>
+        <v>-5.181362958683663</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.067506783370771</v>
+        <v>1.075431336487147</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8293335526847554</v>
+        <v>-0.809522169893818</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.650732812663507</v>
+        <v>2.662619642338069</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.01057466680145</v>
+        <v>-4.990763284010511</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.146561713927668</v>
+        <v>1.154486267044045</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6387338780116025</v>
+        <v>-0.6189224952206651</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.767907678155035</v>
+        <v>2.779794507829597</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.761574868117869</v>
+        <v>-4.741763485326929</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.25906797462476</v>
+        <v>1.266992527741136</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6387338780116025</v>
+        <v>-0.6189224952206651</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.780814019378694</v>
+        <v>2.792700849053256</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.867164857890973</v>
+        <v>-4.847353475100034</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.088856049116299</v>
+        <v>1.096780602232675</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7443238677847068</v>
+        <v>-0.7245124849937694</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.589484095915612</v>
+        <v>2.601370925590175</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.588137562235346</v>
+        <v>-4.568326179444407</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.249011309255636</v>
+        <v>1.256935862372013</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7443238677847068</v>
+        <v>-0.7245124849937694</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.638028437792699</v>
+        <v>2.649915267467261</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.311399387564533</v>
+        <v>-4.291588004773594</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.363085591109956</v>
+        <v>1.371010144226332</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.562507206674781</v>
+        <v>-0.5426958238838436</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.750497446444649</v>
+        <v>2.762384276119211</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.184506981129463</v>
+        <v>-4.164695598338524</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.405128567430506</v>
+        <v>1.413053120546882</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4356148002397111</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.817918904052213</v>
+        <v>2.829805733726775</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.996919473219536</v>
+        <v>-3.977108090428597</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.473202958499384</v>
+        <v>1.48112751161576</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4356148002397111</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.81095829195712</v>
+        <v>2.822845121631682</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.754771079765678</v>
+        <v>-3.734959696974739</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.58452467026207</v>
+        <v>1.592449223378446</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4356148002397111</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.825420646338263</v>
+        <v>2.837307476012825</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.69154170799733</v>
+        <v>-3.67173032520639</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.604348539428604</v>
+        <v>1.612273092544981</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4356148002397111</v>
+        <v>-0.4158034174487737</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.819952766797458</v>
+        <v>2.83183959647202</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.505054015620323</v>
+        <v>-3.485242632829384</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.676441710389984</v>
+        <v>1.68436626350636</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2491271078627049</v>
+        <v>-0.2293157250717675</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.929343476234238</v>
+        <v>2.941230305908801</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.48390481671688</v>
+        <v>-3.464093433925941</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.692602368188687</v>
+        <v>1.700526921305063</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2279779089592615</v>
+        <v>-0.2081665261683241</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.94973397381363</v>
+        <v>2.961620803488192</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.240139374733435</v>
+        <v>-3.220327991942496</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.785889253329115</v>
+        <v>1.793813806445491</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2279779089592615</v>
+        <v>-0.2081665261683241</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.945514682160681</v>
+        <v>2.957401511835243</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.976111307540175</v>
+        <v>-2.956299924749236</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.893624794126435</v>
+        <v>1.901549347242812</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.02611251014330795</v>
+        <v>-0.006301127352370539</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.068758235370269</v>
+        <v>3.080645065044831</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.980720108508027</v>
+        <v>-2.706449530800162</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.884523348722997</v>
+        <v>1.994231579806144</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.02611251014330795</v>
+        <v>-0.006301127352370539</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.061500310353971</v>
+        <v>3.073387140028534</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,19 +45705,19 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.719302572004177</v>
+        <v>3.719302572004175</v>
       </c>
       <c r="C1920" t="n">
         <v>2.989546842497354</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.980720108508027</v>
+        <v>-2.706449530800162</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.884523348722997</v>
+        <v>1.994231579806144</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.02611251014330795</v>
+        <v>-0.006301127352370539</v>
       </c>
       <c r="G1920" t="n">
         <v>2.982610639483722</v>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-32.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-561.6%</t>
+          <t>-590.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-66.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>507.5%</t>
+          <t>498.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-432.2%</t>
+          <t>-448.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-222.3%</t>
+          <t>-230.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-87.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.8%</t>
+          <t>-183.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-283.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-147.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.6%</t>
+          <t>-234.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-147.8%</t>
+          <t>-167.6%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.050027851145666</v>
+        <v>-0.9206180541607403</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.696552702669851</v>
+        <v>2.748316621463821</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9935030990045379</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.713022126844588</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.389186228734188</v>
+        <v>-1.259776431749262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.553973650940891</v>
+        <v>2.605737569734861</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6543447214160159</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.502611399597924</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.717203450461667</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.443105051988668</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3263274996885367</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.326139356300204</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.713866703952696</v>
+        <v>-1.58445690696777</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.452538501000825</v>
+        <v>2.504302419794795</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3290195321075681</v>
+        <v>0.4584293290924942</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.335853326160191</v>
+        <v>3.413499204351147</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.080577755619242</v>
+        <v>-1.951167958634316</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.306960472377939</v>
+        <v>2.358724391171909</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03769151955897754</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.116933087203996</v>
+        <v>3.194578965394952</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.465758146549314</v>
+        <v>-2.336348349564388</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.151430854818773</v>
+        <v>2.203194773612744</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03769151955897754</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.11547562601686</v>
+        <v>3.193121504207815</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.809440919775977</v>
+        <v>-2.680031122791051</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.015726868982724</v>
+        <v>2.067490787776695</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1455975715861957</v>
+        <v>-0.01618777460126958</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.052501118255145</v>
+        <v>3.130146996446101</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.167091270014325</v>
+        <v>-3.037681473029399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.868772787543643</v>
+        <v>1.920536706337613</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5032479218245438</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.834016966768394</v>
+        <v>2.911662844959349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.173752210236473</v>
+        <v>-3.044342413251547</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.867881338155043</v>
+        <v>1.919645256949013</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5032479218245438</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.835789893468653</v>
+        <v>2.913435771659609</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.60555800338626</v>
+        <v>-3.476148206401334</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.681491908362532</v>
+        <v>1.733255827156503</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6396654182658108</v>
+        <v>-0.5102556212808846</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.740272283071298</v>
+        <v>2.817918161262253</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.931990532254004</v>
+        <v>-3.802580735269078</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.539203671817526</v>
+        <v>1.590967590611496</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7221336687729589</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6790761077691</v>
+        <v>2.756721985960055</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.933554683364307</v>
+        <v>-3.804144886379381</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.53715860302937</v>
+        <v>1.58892252182334</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7221336687729589</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.677656699425064</v>
+        <v>2.75530257761602</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.29718092826462</v>
+        <v>-4.167771131279694</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.398195665303486</v>
+        <v>1.449959584097456</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8203553056400847</v>
+        <v>-0.6909455086551586</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.625211277539031</v>
+        <v>2.702857155729986</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.294753863735902</v>
+        <v>-4.165344066750976</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.398421006120805</v>
+        <v>1.450184924914775</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8206880874472364</v>
+        <v>-0.6912782904623102</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.624266123460571</v>
+        <v>2.701912001651527</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.703342640916579</v>
+        <v>-4.573932843931654</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.233747039263293</v>
+        <v>1.285510958057263</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.377874401166923</v>
+        <v>2.455520279357879</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.116325125057673</v>
+        <v>-4.986915328072748</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.063739478078316</v>
+        <v>1.115503396872286</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.373059833638384</v>
+        <v>2.45070571182934</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.532716999344671</v>
+        <v>-5.403307202359746</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8951767789723939</v>
+        <v>0.9469406977663639</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.371053884247261</v>
+        <v>2.448699762438217</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.909394009874515</v>
+        <v>-5.77998421288959</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7547646654291351</v>
+        <v>0.8065285842231051</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.38131257491594</v>
+        <v>2.458958453106896</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.923108874199627</v>
+        <v>-5.793699077214701</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7453782848447861</v>
+        <v>0.7971422036387561</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.377412140061635</v>
+        <v>2.455058018252591</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.235933673444606</v>
+        <v>-6.106523876459681</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6186532852017952</v>
+        <v>0.6704172039957652</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.229276864627915</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.375817060116636</v>
+        <v>2.453462938307592</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.240746711909943</v>
+        <v>-6.111336914925018</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6205070457448683</v>
+        <v>0.6722709645388383</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.378668055224173</v>
+        <v>2.456313933415128</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.674095820020179</v>
+        <v>-6.544686023035254</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4431410979663708</v>
+        <v>0.4949050167603408</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.374641750689769</v>
+        <v>2.452287628880725</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.05709720876281</v>
+        <v>-6.927687411777885</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2898384411477344</v>
+        <v>0.3416023599417044</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.230823499330701</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.374539649368185</v>
+        <v>2.452185527559141</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.432082534934088</v>
+        <v>-7.302672737949162</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1424158266506534</v>
+        <v>0.1941797454446235</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.605808825501978</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.152119969636849</v>
+        <v>2.229765847827805</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.791612857438089</v>
+        <v>-7.662203060453164</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.003954000947103076</v>
+        <v>0.0557179197410731</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.605808825501978</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.1574702729349</v>
+        <v>2.235116151125855</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.118012886103102</v>
+        <v>-7.988603089118177</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1186899905617245</v>
+        <v>-0.06692607176775445</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.932208854166991</v>
+        <v>-1.802799057182065</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96954627569307</v>
+        <v>2.047192153884025</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.111536739309543</v>
+        <v>-7.982126942324618</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.113057781222532</v>
+        <v>-0.06129386242856194</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.925732707373431</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.976473714390974</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.107845814353132</v>
+        <v>-7.978436017368206</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1115814112399676</v>
+        <v>-0.0598174924459971</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.925732707373431</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.976473714390974</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.312103989682996</v>
+        <v>-8.182694192698069</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1877714842532709</v>
+        <v>-0.1360075654593</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.05337165198742</v>
+        <v>-1.923961855002494</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.905403544741223</v>
+        <v>1.983049422932178</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.472743016171361</v>
+        <v>-8.343333219186434</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2475445403641809</v>
+        <v>-0.19578062157021</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.168105124989816</v>
+        <v>-2.03869532800489</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.841046015424222</v>
+        <v>1.918691893615177</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.399273184503912</v>
+        <v>-8.269863387518985</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027849062037799</v>
+        <v>-0.1510209874098094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.094635293322368</v>
+        <v>-1.965225496337441</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.900499615918112</v>
+        <v>1.978145494109068</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.574397601890455</v>
+        <v>-8.444987804905528</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582794524108807</v>
+        <v>-0.2065155336169098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.269759710708911</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.809980186233702</v>
+        <v>1.887626064424658</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.808849695904945</v>
+        <v>-8.679439898920018</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3592794549182723</v>
+        <v>-0.3075155361243018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.269759710708911</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.802761021332106</v>
+        <v>1.880406899523062</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.096653540442183</v>
+        <v>-8.967243743457256</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.481073183507144</v>
+        <v>-0.4293092647131735</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.55756355524615</v>
+        <v>-2.428153758261223</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.623406523835787</v>
+        <v>1.701052402026743</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.326477987606008</v>
+        <v>-9.197068190621081</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5718871725341179</v>
+        <v>-0.520123253740147</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.72021109231631</v>
+        <v>-2.590801295331384</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.526933791432247</v>
+        <v>1.604579669623203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.55850690734227</v>
+        <v>-9.429097110357343</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6620050117995078</v>
+        <v>-0.6102410930055373</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.492419901748308</v>
+        <v>1.570065779939264</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.506491393373457</v>
+        <v>-9.37708159638853</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6372084705255818</v>
+        <v>-0.5854445517316109</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.496410237434709</v>
+        <v>1.574056115625664</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.648163235097577</v>
+        <v>-9.51875343811265</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6953524341139716</v>
+        <v>-0.6435885153200007</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.782223789504733</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.494935010535967</v>
+        <v>1.572580888726923</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.747069975556853</v>
+        <v>-9.617660178571926</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7198617201328097</v>
+        <v>-0.6680978013388388</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.881130529964009</v>
+        <v>-2.751720732979082</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.450644376425274</v>
+        <v>1.52829025461623</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.547917868319754</v>
+        <v>-9.710741164490974</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6532520108846529</v>
+        <v>-0.7183813293531411</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.715808004014196</v>
+        <v>-2.815434676220027</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.536786758348479</v>
+        <v>1.47701075502498</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.322072715600342</v>
+        <v>-9.484896011771564</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5533348767606796</v>
+        <v>-0.6184641952291683</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.673881328427032</v>
+        <v>-2.773508000632864</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.571521836736986</v>
+        <v>1.511745833413487</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.035797903277647</v>
+        <v>-9.198621199448869</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4376858072755425</v>
+        <v>-0.5028151257440316</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.673881328427032</v>
+        <v>-2.773508000632864</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.572660981293045</v>
+        <v>1.512884977969546</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.809002076204314</v>
+        <v>-8.971825372375536</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3443337022841018</v>
+        <v>-0.4094630207525904</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.605767383805488</v>
+        <v>-2.705394056011319</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.616163122228079</v>
+        <v>1.55638711890458</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.525093345275565</v>
+        <v>-8.687916641446787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2250365056739656</v>
+        <v>-0.2901658241424543</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.605767383805488</v>
+        <v>-2.705394056011319</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.621896826466716</v>
+        <v>1.562120823143216</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.278106095082613</v>
+        <v>-8.440929391253835</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1359788679906502</v>
+        <v>-0.2011081864591389</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.458406805818367</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.760351914188621</v>
+        <v>1.700575910865122</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.014269227878543</v>
+        <v>-8.177092524049765</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.04032760242192968</v>
+        <v>-0.1054569208904188</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.458406805818367</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.750468432875714</v>
+        <v>1.690692429552215</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.747027427010146</v>
+        <v>-7.909850723181369</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.06473455742605516</v>
+        <v>-0.0003947610424335224</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.358780133612536</v>
+        <v>-2.458406805818367</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.74863387237634</v>
+        <v>1.688857869052841</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.471218263609662</v>
+        <v>-7.634041559780885</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.1747579078127881</v>
+        <v>0.109628589344299</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.269760825333802</v>
+        <v>-2.369387497539634</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.801745142370119</v>
+        <v>1.741969139046621</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.202150675842683</v>
+        <v>-7.364973972013905</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2830534490650733</v>
+        <v>0.2179241305965847</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.000693237566823</v>
+        <v>-2.100319909772654</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.963854201175801</v>
+        <v>1.904078197852302</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.938090737519887</v>
+        <v>-7.100914033691109</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3754171082324396</v>
+        <v>0.3102877897639509</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.736633299244027</v>
+        <v>-1.836259971449858</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.109029848007726</v>
+        <v>2.049253844684227</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.231011114015049</v>
+        <v>-6.393834410186271</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.655461923974074</v>
+        <v>0.5903326055055853</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.736633299244027</v>
+        <v>-1.836259971449858</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.106242814347425</v>
+        <v>2.046466811023926</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.981370084029097</v>
+        <v>-6.144193380200319</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7556619598562966</v>
+        <v>0.6905326413878075</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.486992269258075</v>
+        <v>-1.586618941463906</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.256371056226838</v>
+        <v>2.196595052903339</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.726828184688021</v>
+        <v>-5.889651480859243</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8568455408134836</v>
+        <v>0.7917162223449949</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.232450369916999</v>
+        <v>-1.332077042122831</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.40846301705224</v>
+        <v>2.348687013728741</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.493346962458422</v>
+        <v>-5.656170258629644</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9581624585431756</v>
+        <v>0.8930331400746865</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9989691476874007</v>
+        <v>-1.098595819893232</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.556476179227852</v>
+        <v>2.496700175904353</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.31363843231455</v>
+        <v>-5.476461728485772</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.027153660287766</v>
+        <v>0.9620243418192764</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9417976435247046</v>
+        <v>-1.041424315730536</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.58788687141251</v>
+        <v>2.528110868089011</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.181362958683663</v>
+        <v>-5.344186254854885</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.075431336487147</v>
+        <v>1.010302018018658</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.809522169893818</v>
+        <v>-0.9091488420996496</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.662619642338069</v>
+        <v>2.60284363901457</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.990763284010511</v>
+        <v>-5.153586580181733</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.154486267044045</v>
+        <v>1.089356948575556</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6189224952206651</v>
+        <v>-0.7185491674264968</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.779794507829597</v>
+        <v>2.720018504506098</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.741763485326929</v>
+        <v>-4.904586781498152</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.266992527741136</v>
+        <v>1.201863209272647</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6189224952206651</v>
+        <v>-0.7185491674264968</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.792700849053256</v>
+        <v>2.732924845729757</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.847353475100034</v>
+        <v>-5.010176771271256</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.096780602232675</v>
+        <v>1.031651283764186</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7245124849937694</v>
+        <v>-0.8241391571996011</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.601370925590175</v>
+        <v>2.541594922266676</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.568326179444407</v>
+        <v>-4.731149475615629</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.256935862372013</v>
+        <v>1.191806543903524</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7245124849937694</v>
+        <v>-0.8241391571996011</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.649915267467261</v>
+        <v>2.590139264143762</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.291588004773594</v>
+        <v>-4.454411300944816</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.371010144226332</v>
+        <v>1.305880825757844</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5426958238838436</v>
+        <v>-0.6423224960896753</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.762384276119211</v>
+        <v>2.702608272795712</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.164695598338524</v>
+        <v>-4.327518894509746</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.413053120546882</v>
+        <v>1.347923802078393</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.5154300896546054</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.829805733726775</v>
+        <v>2.770029730403276</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.977108090428597</v>
+        <v>-4.13993138659982</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.48112751161576</v>
+        <v>1.415998193147271</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.5154300896546054</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.822845121631682</v>
+        <v>2.763069118308183</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.734959696974739</v>
+        <v>-3.897782993145961</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.592449223378446</v>
+        <v>1.527319904909957</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.5154300896546054</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.837307476012825</v>
+        <v>2.777531472689326</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.67173032520639</v>
+        <v>-3.834553621377613</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.612273092544981</v>
+        <v>1.547143774076492</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4158034174487737</v>
+        <v>-0.5154300896546054</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.83183959647202</v>
+        <v>2.772063593148521</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.485242632829384</v>
+        <v>-3.648065929000607</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.68436626350636</v>
+        <v>1.619236945037871</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2293157250717675</v>
+        <v>-0.3289423972775991</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.941230305908801</v>
+        <v>2.881454302585302</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.464093433925941</v>
+        <v>-3.626916730097164</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.700526921305063</v>
+        <v>1.635397602836574</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2081665261683241</v>
+        <v>-0.3077931983741558</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.961620803488192</v>
+        <v>2.901844800164693</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.220327991942496</v>
+        <v>-3.383151288113719</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.793813806445491</v>
+        <v>1.728684487977002</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2081665261683241</v>
+        <v>-0.3077931983741558</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.957401511835243</v>
+        <v>2.897625508511744</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.956299924749236</v>
+        <v>-3.119123220920459</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.901549347242812</v>
+        <v>1.836420028774322</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.006301127352370539</v>
+        <v>-0.1059277995582022</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.080645065044831</v>
+        <v>3.020869061721332</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.706449530800162</v>
+        <v>-2.869272826971385</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.994231579806144</v>
+        <v>1.929102261337654</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.006301127352370539</v>
+        <v>-0.1059277995582022</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.073387140028534</v>
+        <v>3.013611136705034</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.719302572004175</v>
+        <v>3.421064528392216</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.989546842497354</v>
+        <v>2.790712338863007</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.706449530800162</v>
+        <v>-2.869272826971385</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.994231579806144</v>
+        <v>1.929102261337654</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.006301127352370539</v>
+        <v>-0.1059277995582022</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.982610639483722</v>
+        <v>2.783776135849375</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-590.8%</t>
+          <t>-561.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.9%</t>
+          <t>504.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-448.5%</t>
+          <t>-413.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-230.9%</t>
+          <t>-222.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-87.4%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-168.8%</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1237,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-296.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.1%</t>
+          <t>-153.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-234.6%</t>
+          <t>-224.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-167.6%</t>
+          <t>-138.4%</t>
         </is>
       </c>
     </row>
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.389593958375569</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.553810559084338</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.6539369917746349</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.502366761813095</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213499</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.717611180103048</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.442941960132115</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.3259197700471558</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.325894718515376</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.58445690696777</v>
+        <v>-1.714274433594077</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.504302419794795</v>
+        <v>2.452375409144272</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4584293290924942</v>
+        <v>0.3286118024661872</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.413499204351147</v>
+        <v>3.335608688375363</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.951167958634316</v>
+        <v>-2.080985485260623</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.358724391171909</v>
+        <v>2.306797380521386</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.03809924920035845</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.194578965394952</v>
+        <v>3.116688449419168</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.336348349564388</v>
+        <v>-2.466165876190695</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.203194773612744</v>
+        <v>2.15126776296222</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.03809924920035845</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.193121504207815</v>
+        <v>3.115230988232031</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.680031122791051</v>
+        <v>-2.809848649417358</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.067490787776695</v>
+        <v>2.015563777126172</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.01618777460126958</v>
+        <v>-0.1460053012275767</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.130146996446101</v>
+        <v>3.052256480470316</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.037681473029399</v>
+        <v>-3.167498999655706</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.920536706337613</v>
+        <v>1.86860969568709</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5036556514659247</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.911662844959349</v>
+        <v>2.833772328983565</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.044342413251547</v>
+        <v>-3.174159939877854</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.919645256949013</v>
+        <v>1.867718246298491</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5036556514659247</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.913435771659609</v>
+        <v>2.835545255683825</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.476148206401334</v>
+        <v>-3.605965733027642</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.733255827156503</v>
+        <v>1.68132881650598</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5102556212808846</v>
+        <v>-0.6400731479071917</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.817918161262253</v>
+        <v>2.740027645286469</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.802580735269078</v>
+        <v>-3.932398261895385</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.590967590611496</v>
+        <v>1.539040579960973</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7225413984143398</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.756721985960055</v>
+        <v>2.678831469984271</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.804144886379381</v>
+        <v>-3.933962413005688</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.58892252182334</v>
+        <v>1.536995511172817</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7225413984143398</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.75530257761602</v>
+        <v>2.677412061640236</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.167771131279694</v>
+        <v>-4.297588657906001</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.449959584097456</v>
+        <v>1.398032573446934</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6909455086551586</v>
+        <v>-0.8207630352814657</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.702857155729986</v>
+        <v>2.624966639754202</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.165344066750976</v>
+        <v>-4.295161593377283</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.450184924914775</v>
+        <v>1.398257914264252</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6912782904623102</v>
+        <v>-0.8210958170886173</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.701912001651527</v>
+        <v>2.624021485675743</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.573932843931654</v>
+        <v>-4.703750370557961</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.285510958057263</v>
+        <v>1.23358394740674</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.455520279357879</v>
+        <v>2.377629763382095</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.986915328072748</v>
+        <v>-5.116732854699054</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.115503396872286</v>
+        <v>1.063576386221763</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.45070571182934</v>
+        <v>2.372815195853555</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.403307202359746</v>
+        <v>-5.533124728986052</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9469406977663639</v>
+        <v>0.8950136871158416</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.448699762438217</v>
+        <v>2.370809246462433</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.77998421288959</v>
+        <v>-5.909801739515896</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8065285842231051</v>
+        <v>0.7546015735725828</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.458958453106896</v>
+        <v>2.381067937131112</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.793699077214701</v>
+        <v>-5.923516603841008</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7971422036387561</v>
+        <v>0.7452151929882334</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.455058018252591</v>
+        <v>2.377167502276807</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.106523876459681</v>
+        <v>-6.236341403085987</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6704172039957652</v>
+        <v>0.6184901933452425</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.229684594269296</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.453462938307592</v>
+        <v>2.375572422331808</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.111336914925018</v>
+        <v>-6.241154441551324</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6722709645388383</v>
+        <v>0.620343953888316</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.231231228972081</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.456313933415128</v>
+        <v>2.378423417439344</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.544686023035254</v>
+        <v>-6.67450354966156</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4949050167603408</v>
+        <v>0.4429780061098185</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.231231228972081</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.452287628880725</v>
+        <v>2.374397112904941</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.927687411777885</v>
+        <v>-7.057504938404191</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3416023599417044</v>
+        <v>0.2896753492911817</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.231231228972081</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.452185527559141</v>
+        <v>2.374295011583357</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.302672737949162</v>
+        <v>-7.432490264575469</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1941797454446235</v>
+        <v>0.1422527347941012</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.606216555143359</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.229765847827805</v>
+        <v>2.151875331852021</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.662203060453164</v>
+        <v>-7.79202058707947</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0557179197410731</v>
+        <v>0.003790909090550798</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.606216555143359</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.235116151125855</v>
+        <v>2.157225635150071</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.988603089118177</v>
+        <v>-8.118420615744483</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06692607176775445</v>
+        <v>-0.1188530824182772</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.802799057182065</v>
+        <v>-1.932616583808372</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.047192153884025</v>
+        <v>1.969301637908241</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.982126942324618</v>
+        <v>-8.111944468950924</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06129386242856194</v>
+        <v>-0.1132208730790842</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.926140437014812</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.05411959258193</v>
+        <v>1.976229076606145</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.978436017368206</v>
+        <v>-8.108253543994513</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.0598174924459971</v>
+        <v>-0.1117445030965203</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.926140437014812</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.05411959258193</v>
+        <v>1.976229076606145</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.182694192698069</v>
+        <v>-8.312511719324377</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360075654593</v>
+        <v>-0.1879345761098232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.923961855002494</v>
+        <v>-2.053779381628801</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.983049422932178</v>
+        <v>1.905158906956395</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.343333219186434</v>
+        <v>-8.473150745812742</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.19578062157021</v>
+        <v>-0.2477076322207332</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.03869532800489</v>
+        <v>-2.168512854631197</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.918691893615177</v>
+        <v>1.840801377639393</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.269863387518985</v>
+        <v>-8.399680914145293</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1510209874098094</v>
+        <v>-0.2029479980603326</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.965225496337441</v>
+        <v>-2.095043022963748</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978145494109068</v>
+        <v>1.900254978133283</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.444987804905528</v>
+        <v>-8.574805331531836</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2065155336169098</v>
+        <v>-0.258442544267433</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.270167440350292</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.887626064424658</v>
+        <v>1.809735548448874</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.679439898920018</v>
+        <v>-8.809257425546326</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3075155361243018</v>
+        <v>-0.359442546774825</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.270167440350292</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.880406899523062</v>
+        <v>1.802516383547278</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.967243743457256</v>
+        <v>-9.097061270083564</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4293092647131735</v>
+        <v>-0.4812362753636967</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.428153758261223</v>
+        <v>-2.55797128488753</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.701052402026743</v>
+        <v>1.623161886050959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.197068190621081</v>
+        <v>-9.326885717247389</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.520123253740147</v>
+        <v>-0.5720502643906702</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.590801295331384</v>
+        <v>-2.720618821957691</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.604579669623203</v>
+        <v>1.526689153647419</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.429097110357343</v>
+        <v>-9.558914636983651</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6102410930055373</v>
+        <v>-0.6621681036560605</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782631519146114</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.570065779939264</v>
+        <v>1.49217526396348</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.37708159638853</v>
+        <v>-9.506899123014838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5854445517316109</v>
+        <v>-0.6373715623821341</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782631519146114</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.574056115625664</v>
+        <v>1.49616559964988</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.51875343811265</v>
+        <v>-9.648570964738958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6435885153200007</v>
+        <v>-0.6955155259705239</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.782631519146114</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.572580888726923</v>
+        <v>1.494690372751139</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.617660178571926</v>
+        <v>-9.747477705198234</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6680978013388388</v>
+        <v>-0.720024811989362</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.751720732979082</v>
+        <v>-2.881538259605389</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.52829025461623</v>
+        <v>1.450399738640446</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.710741164490974</v>
+        <v>-9.548325597961135</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7183813293531411</v>
+        <v>-0.6534151027412052</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.815434676220027</v>
+        <v>-2.716215733655576</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.47701075502498</v>
+        <v>1.536542120563651</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.484896011771564</v>
+        <v>-9.322480445241723</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6184641952291683</v>
+        <v>-0.5534979686172319</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.773508000632864</v>
+        <v>-2.674289058068412</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.511745833413487</v>
+        <v>1.571277198952158</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.198621199448869</v>
+        <v>-9.036205632919028</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5028151257440316</v>
+        <v>-0.4378488991320952</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.773508000632864</v>
+        <v>-2.674289058068412</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.512884977969546</v>
+        <v>1.572416343508217</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.971825372375536</v>
+        <v>-8.809409805845695</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4094630207525904</v>
+        <v>-0.344496794140654</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.705394056011319</v>
+        <v>-2.606175113446868</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.55638711890458</v>
+        <v>1.615918484443251</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.687916641446787</v>
+        <v>-8.525501074916946</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2901658241424543</v>
+        <v>-0.2251995975305179</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.705394056011319</v>
+        <v>-2.606175113446868</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.562120823143216</v>
+        <v>1.621652188681887</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.440929391253835</v>
+        <v>-8.278513824723994</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2011081864591389</v>
+        <v>-0.1361419598472025</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.458406805818367</v>
+        <v>-2.359187863253916</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.700575910865122</v>
+        <v>1.760107276403793</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.177092524049765</v>
+        <v>-8.014676957519924</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1054569208904188</v>
+        <v>-0.0404906942784824</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.458406805818367</v>
+        <v>-2.359187863253916</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.690692429552215</v>
+        <v>1.750223795090886</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.909850723181369</v>
+        <v>-7.747435156651528</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.0003947610424335224</v>
+        <v>0.06457146556950288</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.458406805818367</v>
+        <v>-2.359187863253916</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.688857869052841</v>
+        <v>1.748389234591512</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.634041559780885</v>
+        <v>-7.471625993251044</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.109628589344299</v>
+        <v>0.1745948159562354</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.369387497539634</v>
+        <v>-2.270168554975182</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.741969139046621</v>
+        <v>1.801500504585291</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.364973972013905</v>
+        <v>-7.202558405484064</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2179241305965847</v>
+        <v>0.2828903572085211</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.100319909772654</v>
+        <v>-2.001100967208203</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.904078197852302</v>
+        <v>1.963609563390972</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.100914033691109</v>
+        <v>-6.938498467161268</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3102877897639509</v>
+        <v>0.3752540163758873</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.836259971449858</v>
+        <v>-1.737041028885407</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.049253844684227</v>
+        <v>2.108785210222898</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.393834410186271</v>
+        <v>-6.23141884365643</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.5903326055055853</v>
+        <v>0.6552988321175217</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.836259971449858</v>
+        <v>-1.737041028885407</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.046466811023926</v>
+        <v>2.105998176562597</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.144193380200319</v>
+        <v>-5.981777813670478</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.6905326413878075</v>
+        <v>0.7554988679997439</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.586618941463906</v>
+        <v>-1.487399998899455</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.196595052903339</v>
+        <v>2.25612641844201</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.889651480859243</v>
+        <v>-5.727235914329402</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.7917162223449949</v>
+        <v>0.8566824489569314</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.332077042122831</v>
+        <v>-1.23285809955838</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.348687013728741</v>
+        <v>2.408218379267412</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.656170258629644</v>
+        <v>-5.493754692099803</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.8930331400746865</v>
+        <v>0.9579993666866229</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.098595819893232</v>
+        <v>-0.999376877328781</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.496700175904353</v>
+        <v>2.556231541443023</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.476461728485772</v>
+        <v>-5.314046161955931</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.9620243418192764</v>
+        <v>1.026990568431213</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.041424315730536</v>
+        <v>-0.9422053731660849</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.528110868089011</v>
+        <v>2.587642233627682</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.344186254854885</v>
+        <v>-5.181770688325044</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.010302018018658</v>
+        <v>1.075268244630594</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9091488420996496</v>
+        <v>-0.8099298995351982</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.60284363901457</v>
+        <v>2.662375004553241</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.153586580181733</v>
+        <v>-4.991171013651892</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.089356948575556</v>
+        <v>1.154323175187492</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7185491674264968</v>
+        <v>-0.6193302248620454</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.720018504506098</v>
+        <v>2.779549870044769</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.904586781498152</v>
+        <v>-4.742171214968311</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.201863209272647</v>
+        <v>1.266829435884584</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7185491674264968</v>
+        <v>-0.6193302248620454</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.732924845729757</v>
+        <v>2.792456211268428</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.010176771271256</v>
+        <v>-4.847761204741415</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.031651283764186</v>
+        <v>1.096617510376123</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8241391571996011</v>
+        <v>-0.7249202146351497</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.541594922266676</v>
+        <v>2.601126287805347</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.731149475615629</v>
+        <v>-4.568733909085788</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.191806543903524</v>
+        <v>1.25677277051546</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8241391571996011</v>
+        <v>-0.7249202146351497</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.590139264143762</v>
+        <v>2.649670629682433</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.454411300944816</v>
+        <v>-4.291995734414975</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.305880825757844</v>
+        <v>1.37084705236978</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6423224960896753</v>
+        <v>-0.5431035535252239</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.702608272795712</v>
+        <v>2.762139638334383</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.327518894509746</v>
+        <v>-4.165103327979905</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.347923802078393</v>
+        <v>1.41289002869033</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5154300896546054</v>
+        <v>-0.4162111470901539</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.770029730403276</v>
+        <v>2.829561095941947</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.13993138659982</v>
+        <v>-3.977515820069978</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.415998193147271</v>
+        <v>1.480964419759208</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5154300896546054</v>
+        <v>-0.4162111470901539</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.763069118308183</v>
+        <v>2.822600483846854</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.897782993145961</v>
+        <v>-3.73536742661612</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.527319904909957</v>
+        <v>1.592286131521894</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5154300896546054</v>
+        <v>-0.4162111470901539</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.777531472689326</v>
+        <v>2.837062838227997</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.834553621377613</v>
+        <v>-3.672138054847772</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.547143774076492</v>
+        <v>1.612110000688428</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5154300896546054</v>
+        <v>-0.4162111470901539</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.772063593148521</v>
+        <v>2.831594958687192</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.648065929000607</v>
+        <v>-3.485650362470765</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.619236945037871</v>
+        <v>1.684203171649808</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3289423972775991</v>
+        <v>-0.2297234547131477</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.881454302585302</v>
+        <v>2.940985668123973</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.626916730097164</v>
+        <v>-3.464501163567322</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.635397602836574</v>
+        <v>1.700363829448511</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3077931983741558</v>
+        <v>-0.2085742558097043</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.901844800164693</v>
+        <v>2.961376165703364</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.383151288113719</v>
+        <v>-3.220735721583877</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.728684487977002</v>
+        <v>1.793650714588939</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3077931983741558</v>
+        <v>-0.2085742558097043</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.897625508511744</v>
+        <v>2.957156874050415</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.119123220920459</v>
+        <v>-2.956707654390617</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.836420028774322</v>
+        <v>1.901386255386259</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1059277995582022</v>
+        <v>-0.006708856993750789</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.020869061721332</v>
+        <v>3.080400427260003</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.869272826971385</v>
+        <v>-2.593200251254834</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.929102261337654</v>
+        <v>2.039531291624275</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1059277995582022</v>
+        <v>-0.006708856993750789</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.013611136705034</v>
+        <v>3.073142502243705</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.421064528392216</v>
+        <v>3.733045231115174</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.790712338863007</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.869272826971385</v>
+        <v>-2.515255939128522</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.929102261337654</v>
+        <v>2.074308139995448</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1059277995582022</v>
+        <v>-0.006708856993750789</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.783776135849375</v>
+        <v>3.076741625764354</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240331.xlsx
+++ b/tame_output/ON/bt/strategyON_20240331.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-68.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-62.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>504.2%</t>
+          <t>499.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-413.1%</t>
+          <t>-410.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-222.3%</t>
+          <t>-219.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-168.8%</t>
+          <t>-167.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-283.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.2%</t>
+          <t>-148.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.7%</t>
+          <t>-211.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.4%</t>
+          <t>-130.6%</t>
         </is>
       </c>
     </row>
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.389593958375569</v>
+        <v>-1.259776431749262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.553810559084338</v>
+        <v>2.605737569734861</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6539369917746349</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.502366761813095</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.717611180103048</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.442941960132115</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3259197700471558</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.325894718515376</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.714274433594077</v>
+        <v>-1.58445690696777</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.452375409144272</v>
+        <v>2.504302419794795</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3286118024661872</v>
+        <v>0.4584293290924942</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.335608688375363</v>
+        <v>3.413499204351147</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.080985485260623</v>
+        <v>-1.951167958634316</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.306797380521386</v>
+        <v>2.358724391171909</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03809924920035845</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.116688449419168</v>
+        <v>3.194578965394952</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.466165876190695</v>
+        <v>-2.336348349564388</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.15126776296222</v>
+        <v>2.203194773612744</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03809924920035845</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.115230988232031</v>
+        <v>3.193121504207815</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.809848649417358</v>
+        <v>-2.680031122791051</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.015563777126172</v>
+        <v>2.067490787776695</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1460053012275767</v>
+        <v>-0.01618777460126958</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.052256480470316</v>
+        <v>3.130146996446101</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.167498999655706</v>
+        <v>-3.037681473029399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.86860969568709</v>
+        <v>1.920536706337613</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5036556514659247</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.833772328983565</v>
+        <v>2.911662844959349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.174159939877854</v>
+        <v>-3.044342413251547</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.867718246298491</v>
+        <v>1.919645256949013</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5036556514659247</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.835545255683825</v>
+        <v>2.913435771659609</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.605965733027642</v>
+        <v>-3.476148206401334</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.68132881650598</v>
+        <v>1.733255827156503</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6400731479071917</v>
+        <v>-0.5102556212808846</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.740027645286469</v>
+        <v>2.817918161262253</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.932398261895385</v>
+        <v>-3.802580735269078</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.539040579960973</v>
+        <v>1.590967590611496</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7225413984143398</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.678831469984271</v>
+        <v>2.756721985960055</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.933962413005688</v>
+        <v>-3.804144886379381</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.536995511172817</v>
+        <v>1.58892252182334</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7225413984143398</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.677412061640236</v>
+        <v>2.75530257761602</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.297588657906001</v>
+        <v>-4.167771131279694</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.398032573446934</v>
+        <v>1.449959584097456</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8207630352814657</v>
+        <v>-0.6909455086551586</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.624966639754202</v>
+        <v>2.702857155729986</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.295161593377283</v>
+        <v>-4.165344066750976</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.398257914264252</v>
+        <v>1.450184924914775</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8210958170886173</v>
+        <v>-0.6912782904623102</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.624021485675743</v>
+        <v>2.701912001651527</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.703750370557961</v>
+        <v>-4.573932843931654</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.23358394740674</v>
+        <v>1.285510958057263</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.377629763382095</v>
+        <v>2.455520279357879</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.116732854699054</v>
+        <v>-4.986915328072748</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.063576386221763</v>
+        <v>1.115503396872286</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.372815195853555</v>
+        <v>2.45070571182934</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.533124728986052</v>
+        <v>-5.403307202359746</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8950136871158416</v>
+        <v>0.9469406977663639</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.370809246462433</v>
+        <v>2.448699762438217</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.909801739515896</v>
+        <v>-5.77998421288959</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7546015735725828</v>
+        <v>0.8065285842231051</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.381067937131112</v>
+        <v>2.458958453106896</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.923516603841008</v>
+        <v>-5.793699077214701</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7452151929882334</v>
+        <v>0.7971422036387561</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.377167502276807</v>
+        <v>2.455058018252591</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.236341403085987</v>
+        <v>-6.106523876459681</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6184901933452425</v>
+        <v>0.6704172039957652</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.229684594269296</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.375572422331808</v>
+        <v>2.453462938307592</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.241154441551324</v>
+        <v>-6.111336914925018</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.620343953888316</v>
+        <v>0.6722709645388383</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.231231228972081</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.378423417439344</v>
+        <v>2.456313933415128</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.67450354966156</v>
+        <v>-6.544686023035254</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4429780061098185</v>
+        <v>0.4949050167603408</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.231231228972081</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.374397112904941</v>
+        <v>2.452287628880725</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.057504938404191</v>
+        <v>-6.927687411777885</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2896753492911817</v>
+        <v>0.3416023599417044</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.231231228972081</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.374295011583357</v>
+        <v>2.452185527559141</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.432490264575469</v>
+        <v>-7.302672737949162</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1422527347941012</v>
+        <v>0.1941797454446235</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.606216555143359</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.151875331852021</v>
+        <v>2.229765847827805</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.79202058707947</v>
+        <v>-7.662203060453164</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.003790909090550798</v>
+        <v>0.0557179197410731</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.606216555143359</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.157225635150071</v>
+        <v>2.235116151125855</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.118420615744483</v>
+        <v>-7.988603089118177</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1188530824182772</v>
+        <v>-0.06692607176775445</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.932616583808372</v>
+        <v>-1.802799057182065</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.969301637908241</v>
+        <v>2.047192153884025</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.111944468950924</v>
+        <v>-7.982126942324618</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1132208730790842</v>
+        <v>-0.06129386242856194</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.926140437014812</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.976229076606145</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.108253543994513</v>
+        <v>-7.978436017368206</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1117445030965203</v>
+        <v>-0.0598174924459971</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.926140437014812</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.976229076606145</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.312511719324377</v>
+        <v>-8.182694192698069</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1879345761098232</v>
+        <v>-0.1360075654593</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.053779381628801</v>
+        <v>-1.923961855002494</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.905158906956395</v>
+        <v>1.983049422932178</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.473150745812742</v>
+        <v>-8.343333219186434</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2477076322207332</v>
+        <v>-0.19578062157021</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.168512854631197</v>
+        <v>-2.03869532800489</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.840801377639393</v>
+        <v>1.918691893615177</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.399680914145293</v>
+        <v>-8.269863387518985</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2029479980603326</v>
+        <v>-0.1510209874098094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.095043022963748</v>
+        <v>-1.965225496337441</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.900254978133283</v>
+        <v>1.978145494109068</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.574805331531836</v>
+        <v>-8.444987804905528</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.258442544267433</v>
+        <v>-0.2065155336169098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.270167440350292</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.809735548448874</v>
+        <v>1.887626064424658</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.809257425546326</v>
+        <v>-8.679439898920018</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359442546774825</v>
+        <v>-0.3075155361243018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.270167440350292</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.802516383547278</v>
+        <v>1.880406899523062</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.097061270083564</v>
+        <v>-8.967243743457256</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4812362753636967</v>
+        <v>-0.4293092647131735</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.55797128488753</v>
+        <v>-2.428153758261223</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.623161886050959</v>
+        <v>1.701052402026743</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.326885717247389</v>
+        <v>-9.197068190621081</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5720502643906702</v>
+        <v>-0.520123253740147</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.720618821957691</v>
+        <v>-2.590801295331384</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.526689153647419</v>
+        <v>1.604579669623203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.558914636983651</v>
+        <v>-9.429097110357343</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6621681036560605</v>
+        <v>-0.6102410930055373</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.782631519146114</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.49217526396348</v>
+        <v>1.570065779939264</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.506899123014838</v>
+        <v>-9.37708159638853</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6373715623821341</v>
+        <v>-0.5854445517316109</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.782631519146114</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.49616559964988</v>
+        <v>1.574056115625664</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.648570964738958</v>
+        <v>-9.51875343811265</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6955155259705239</v>
+        <v>-0.6435885153200007</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.782631519146114</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.494690372751139</v>
+        <v>1.572580888726923</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.747477705198234</v>
+        <v>-9.617660178571926</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.720024811989362</v>
+        <v>-0.6680978013388388</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.881538259605389</v>
+        <v>-2.751720732979082</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.450399738640446</v>
+        <v>1.52829025461623</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.548325597961135</v>
+        <v>-9.418508071334827</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6534151027412052</v>
+        <v>-0.601488092090682</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.716215733655576</v>
+        <v>-2.586398207029269</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.536542120563651</v>
+        <v>1.614432636539435</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.322480445241723</v>
+        <v>-9.192662918615415</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5534979686172319</v>
+        <v>-0.5015709579667087</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.674289058068412</v>
+        <v>-2.544471531442105</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.571277198952158</v>
+        <v>1.649167714927942</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.036205632919028</v>
+        <v>-8.90638810629272</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4378488991320952</v>
+        <v>-0.3859218884815721</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.674289058068412</v>
+        <v>-2.544471531442105</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.572416343508217</v>
+        <v>1.650306859484001</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.809409805845695</v>
+        <v>-8.679592279219387</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.344496794140654</v>
+        <v>-0.2925697834901309</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.606175113446868</v>
+        <v>-2.476357586820561</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.615918484443251</v>
+        <v>1.693809000419035</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.525501074916946</v>
+        <v>-8.395683548290638</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2251995975305179</v>
+        <v>-0.1732725868799947</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.606175113446868</v>
+        <v>-2.476357586820561</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.621652188681887</v>
+        <v>1.699542704657672</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.278513824723994</v>
+        <v>-8.148696298097686</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1361419598472025</v>
+        <v>-0.08421494919667927</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.359187863253916</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.760107276403793</v>
+        <v>1.837997792379578</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.014676957519924</v>
+        <v>-7.884859430893617</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.0404906942784824</v>
+        <v>0.01143631637204079</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.359187863253916</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.750223795090886</v>
+        <v>1.82811431106667</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.747435156651528</v>
+        <v>-7.617617630025221</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.06457146556950288</v>
+        <v>0.1164984762200256</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.359187863253916</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.748389234591512</v>
+        <v>1.826279750567296</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.471625993251044</v>
+        <v>-7.341808466624737</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.1745948159562354</v>
+        <v>0.2265218266067586</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.270168554975182</v>
+        <v>-2.140351028348875</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.801500504585291</v>
+        <v>1.879391020561076</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.202558405484064</v>
+        <v>-7.072740878857757</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2828903572085211</v>
+        <v>0.3348173678590438</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.001100967208203</v>
+        <v>-1.871283440581896</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.963609563390972</v>
+        <v>2.041500079366757</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.938498467161268</v>
+        <v>-6.808680940534961</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3752540163758873</v>
+        <v>0.42718102702641</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.737041028885407</v>
+        <v>-1.6072235022591</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.108785210222898</v>
+        <v>2.186675726198682</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.23141884365643</v>
+        <v>-6.101601317030123</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6552988321175217</v>
+        <v>0.7072258427680445</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.737041028885407</v>
+        <v>-1.6072235022591</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.105998176562597</v>
+        <v>2.183888692538381</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.981777813670478</v>
+        <v>-5.851960287044171</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7554988679997439</v>
+        <v>0.8074258786502666</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.487399998899455</v>
+        <v>-1.357582472273148</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.25612641844201</v>
+        <v>2.334016934417794</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.727235914329402</v>
+        <v>-5.597418387703096</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8566824489569314</v>
+        <v>0.9086094596074537</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.23285809955838</v>
+        <v>-1.103040572932072</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.408218379267412</v>
+        <v>2.486108895243196</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.493754692099803</v>
+        <v>-5.363937165473497</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9579993666866229</v>
+        <v>1.009926377337146</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.999376877328781</v>
+        <v>-0.8695593507024739</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.556231541443023</v>
+        <v>2.634122057418808</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.314046161955931</v>
+        <v>-5.184228635329625</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.026990568431213</v>
+        <v>1.078917579081736</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9422053731660849</v>
+        <v>-0.8123878465397778</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.587642233627682</v>
+        <v>2.665532749603466</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.181770688325044</v>
+        <v>-5.051953161698738</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.075268244630594</v>
+        <v>1.127195255281117</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8099298995351982</v>
+        <v>-0.6801123729088911</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.662375004553241</v>
+        <v>2.740265520529025</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.991171013651892</v>
+        <v>-4.861353487025585</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.154323175187492</v>
+        <v>1.206250185838015</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6193302248620454</v>
+        <v>-0.4895126982357383</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.779549870044769</v>
+        <v>2.857440386020554</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.742171214968311</v>
+        <v>-4.612353688342004</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.266829435884584</v>
+        <v>1.318756446535106</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6193302248620454</v>
+        <v>-0.4895126982357383</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.792456211268428</v>
+        <v>2.870346727244212</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.847761204741415</v>
+        <v>-4.717943678115109</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.096617510376123</v>
+        <v>1.148544521026645</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7249202146351497</v>
+        <v>-0.5951026880088426</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.601126287805347</v>
+        <v>2.679016803781131</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.568733909085788</v>
+        <v>-4.743598319552553</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.25677277051546</v>
+        <v>1.186827006328754</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7249202146351497</v>
+        <v>-0.5951026880088426</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.649670629682433</v>
+        <v>2.727561145658217</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.291995734414975</v>
+        <v>-4.466860144881741</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.37084705236978</v>
+        <v>1.300901288183074</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5431035535252239</v>
+        <v>-0.4132860268989168</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.762139638334383</v>
+        <v>2.840030154310167</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.165103327979905</v>
+        <v>-4.339967738446671</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.41289002869033</v>
+        <v>1.342944264503624</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4162111470901539</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.829561095941947</v>
+        <v>2.907451611917731</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.977515820069978</v>
+        <v>-4.152380230536744</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.480964419759208</v>
+        <v>1.411018655572501</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4162111470901539</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.822600483846854</v>
+        <v>2.900490999822638</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.73536742661612</v>
+        <v>-3.910231837082886</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.592286131521894</v>
+        <v>1.522340367335187</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4162111470901539</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.837062838227997</v>
+        <v>2.914953354203781</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.672138054847772</v>
+        <v>-3.847002465314538</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.612110000688428</v>
+        <v>1.542164236501722</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4162111470901539</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.831594958687192</v>
+        <v>2.909485474662976</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.485650362470765</v>
+        <v>-3.660514772937532</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.684203171649808</v>
+        <v>1.614257407463101</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2297234547131477</v>
+        <v>-0.09990592808684062</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.940985668123973</v>
+        <v>3.018876184099757</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.464501163567322</v>
+        <v>-3.639365574034088</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.700363829448511</v>
+        <v>1.630418065261804</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2085742558097043</v>
+        <v>-0.07875672918339727</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.961376165703364</v>
+        <v>3.039266681679148</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.220735721583877</v>
+        <v>-3.395600132050644</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.793650714588939</v>
+        <v>1.723704950402232</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2085742558097043</v>
+        <v>-0.07875672918339727</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.957156874050415</v>
+        <v>3.035047390026199</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.956707654390617</v>
+        <v>-3.131572064857384</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.901386255386259</v>
+        <v>1.831440491199552</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.006708856993750789</v>
+        <v>0.1231086696325563</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.080400427260003</v>
+        <v>3.158290943235787</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.593200251254834</v>
+        <v>-2.789402084066082</v>
       </c>
       <c r="E1919" t="n">
-        <v>2.039531291624275</v>
+        <v>1.961050558499775</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.006708856993750789</v>
+        <v>0.1231086696325563</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.073142502243705</v>
+        <v>3.151033018219489</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.733045231115174</v>
+        <v>3.392283094512424</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.515255939128522</v>
+        <v>-2.49025786615141</v>
       </c>
       <c r="E1920" t="n">
-        <v>2.074308139995448</v>
+        <v>2.084307369186293</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.006708856993750789</v>
+        <v>0.1231086696325563</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.076741625764354</v>
+        <v>3.154632141740138</v>
       </c>
     </row>
   </sheetData>
